--- a/Unity/Assets/Config/Excel/DropConfig.xlsx
+++ b/Unity/Assets/Config/Excel/DropConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -63,6 +63,18 @@
   </si>
   <si>
     <t>100;10003001;1;1@100;10003002;1;1</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>10;10002001;1;1@10;10002002;1;1@10;10002003;1;1@10;10002004;1;1@10;10002005;1;1@10;10002006;1;1@100;10001011;1;1</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>100;10002001;1;1@100;10002002;1;1@100;10002003;1;1@100;10002004;1;1@100;10002005;1;1@100;10002006;1;1</t>
   </si>
 </sst>
 </file>
@@ -1095,12 +1107,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.875" style="2"/>
-    <col min="3" max="3" width="106.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="176.625" style="2" customWidth="1"/>
     <col min="4" max="16380" width="17.875" style="2"/>
     <col min="16381" max="16384" width="17.875" style="3"/>
   </cols>
@@ -1154,6 +1166,22 @@
         <v>11</v>
       </c>
     </row>
+    <row r="6" customHeight="1" spans="2:3">
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:3">
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Unity/Assets/Config/Excel/DropConfig.xlsx
+++ b/Unity/Assets/Config/Excel/DropConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1150,7 +1150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:3">
+    <row r="4" customHeight="1" spans="1:3">
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:3">
+    <row r="5" customHeight="1" spans="1:3">
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:3">
+    <row r="6" customHeight="1" spans="1:3">
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:3">
+    <row r="7" customHeight="1" spans="1:3">
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
